--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.21459520879934</v>
+        <v>7.347371721429893</v>
       </c>
       <c r="D2" t="n">
-        <v>46.72746632189553</v>
+        <v>7.593213277308024</v>
       </c>
       <c r="E2" t="n">
-        <v>13.97666016082271</v>
+        <v>2.27120727613369</v>
       </c>
       <c r="F2" t="n">
-        <v>14.60339150239346</v>
+        <v>2.373051119138936</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.65235885257742</v>
+        <v>4.168508313543831</v>
       </c>
       <c r="D3" t="n">
-        <v>24.95221951231823</v>
+        <v>4.054735670751713</v>
       </c>
       <c r="E3" t="n">
-        <v>13.97666016082271</v>
+        <v>2.27120727613369</v>
       </c>
       <c r="F3" t="n">
-        <v>14.60339150239346</v>
+        <v>2.373051119138936</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.10138272732927</v>
+        <v>1.803974693191006</v>
       </c>
       <c r="D4" t="n">
-        <v>11.26252278326615</v>
+        <v>1.830159952280749</v>
       </c>
       <c r="E4" t="n">
-        <v>13.97666016082271</v>
+        <v>2.27120727613369</v>
       </c>
       <c r="F4" t="n">
-        <v>14.60339150239346</v>
+        <v>2.373051119138936</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
